--- a/KAMCHATKA_ZAPOLNENIE/05_АО_Благовещенский_арматурный_завод.xlsx
+++ b/KAMCHATKA_ZAPOLNENIE/05_АО_Благовещенский_арматурный_завод.xlsx
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AE14"/>
+  <dimension ref="A1:AE15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -598,7 +598,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Нацрежим ПП 1875 (ограничение): обязательны производитель, страна и ДЕЙСТВУЮЩИЙ номер реестровой записи ПП 719 (для ЕАЭС — евразийский реестр). Приложите выписку из ГИСП и сертификаты. Доставка — до Петропавловска-Камчатского (укажите вес).</t>
+          <t>Графы марка / производитель / страна / № записи частично ПРЕДЗАПОЛНЕНЫ нами по вашему КП и открытым данным — проверьте и исправьте, если не так.</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -632,358 +632,291 @@
       <c r="AD3" s="2" t="n"/>
       <c r="AE3" s="2" t="n"/>
     </row>
-    <row r="4" ht="66" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Нацрежим ПП 1875 (ограничение): обязательны производитель, страна и ДЕЙСТВУЮЩИЙ номер реестровой записи ПП 719 (для ЕАЭС — евразийский реестр). Приложите выписку из ГИСП и сертификаты. Доставка — до Петропавловска-Камчатского (укажите вес).</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="2" t="n"/>
+      <c r="L4" s="2" t="n"/>
+      <c r="M4" s="2" t="n"/>
+      <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="n"/>
+      <c r="P4" s="2" t="n"/>
+      <c r="Q4" s="2" t="n"/>
+      <c r="R4" s="2" t="n"/>
+      <c r="S4" s="2" t="n"/>
+      <c r="T4" s="2" t="n"/>
+      <c r="U4" s="2" t="n"/>
+      <c r="V4" s="2" t="n"/>
+      <c r="W4" s="2" t="n"/>
+      <c r="X4" s="2" t="n"/>
+      <c r="Y4" s="2" t="n"/>
+      <c r="Z4" s="2" t="n"/>
+      <c r="AA4" s="2" t="n"/>
+      <c r="AB4" s="2" t="n"/>
+      <c r="AC4" s="2" t="n"/>
+      <c r="AD4" s="2" t="n"/>
+      <c r="AE4" s="2" t="n"/>
+    </row>
+    <row r="5" ht="66" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>№</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Табл./№ ТЗ</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>ГОСТ/ТУ</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>Ду, мм</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Проход</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Давление, МПа</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Температура, °С</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>Среда</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>Материал корпуса</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>Климатическое исполнение</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>Присоединение</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>Приводное устройство: наименование</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>Приводное устройство: технические характеристики</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
+      <c r="O5" s="3" t="inlineStr">
         <is>
           <t>Установочное положение</t>
         </is>
       </c>
-      <c r="P4" s="3" t="inlineStr">
+      <c r="P5" s="3" t="inlineStr">
         <is>
           <t>Материал штока, шара, уплотнений</t>
         </is>
       </c>
-      <c r="Q4" s="3" t="inlineStr">
+      <c r="Q5" s="3" t="inlineStr">
         <is>
           <t>Габариты</t>
         </is>
       </c>
-      <c r="R4" s="3" t="inlineStr">
+      <c r="R5" s="3" t="inlineStr">
         <is>
           <t>Примечание</t>
         </is>
       </c>
-      <c r="S4" s="3" t="inlineStr">
+      <c r="S5" s="3" t="inlineStr">
         <is>
           <t>Кол-во</t>
         </is>
       </c>
-      <c r="T4" s="3" t="inlineStr">
+      <c r="T5" s="3" t="inlineStr">
         <is>
           <t>Ед.</t>
         </is>
       </c>
-      <c r="U4" s="4" t="inlineStr">
+      <c r="U5" s="4" t="inlineStr">
         <is>
           <t>Предлагаемая марка / обозначение</t>
         </is>
       </c>
-      <c r="V4" s="4" t="inlineStr">
+      <c r="V5" s="4" t="inlineStr">
         <is>
           <t>Производитель (завод)</t>
         </is>
       </c>
-      <c r="W4" s="4" t="inlineStr">
+      <c r="W5" s="4" t="inlineStr">
         <is>
           <t>Страна происхождения</t>
         </is>
       </c>
-      <c r="X4" s="4" t="inlineStr">
+      <c r="X5" s="4" t="inlineStr">
         <is>
           <t>№ реестровой записи (ПП 719) или евразийского реестра</t>
         </is>
       </c>
-      <c r="Y4" s="4" t="inlineStr">
+      <c r="Y5" s="4" t="inlineStr">
         <is>
           <t>Срок действия записи</t>
         </is>
       </c>
-      <c r="Z4" s="4" t="inlineStr">
+      <c r="Z5" s="4" t="inlineStr">
         <is>
           <t>Соответствие ТЗ: «да» или отличия</t>
         </is>
       </c>
-      <c r="AA4" s="4" t="inlineStr">
+      <c r="AA5" s="4" t="inlineStr">
         <is>
           <t>Цена за ед. с НДС, ₽</t>
         </is>
       </c>
-      <c r="AB4" s="4" t="inlineStr">
+      <c r="AB5" s="4" t="inlineStr">
         <is>
           <t>Сумма с НДС, ₽</t>
         </is>
       </c>
-      <c r="AC4" s="4" t="inlineStr">
+      <c r="AC5" s="4" t="inlineStr">
         <is>
           <t>Срок отгрузки</t>
         </is>
       </c>
-      <c r="AD4" s="4" t="inlineStr">
+      <c r="AD5" s="4" t="inlineStr">
         <is>
           <t>Вес ед., кг / габариты</t>
         </is>
       </c>
-      <c r="AE4" s="4" t="inlineStr">
+      <c r="AE5" s="4" t="inlineStr">
         <is>
           <t>Сертификат / декларация ТР ТС №</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>1.1/2</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Клапан запорный 15нж65нж Ду 200 Ру 16</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>ТУ 3700-001-66364836-2010</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>Полнопроходной</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>до +6000С</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>вода, пар</t>
-        </is>
-      </c>
-      <c r="J5" s="6" t="inlineStr">
-        <is>
-          <t>12Х18Н10Т</t>
-        </is>
-      </c>
-      <c r="K5" s="6" t="inlineStr">
-        <is>
-          <t>УХЛ1</t>
-        </is>
-      </c>
-      <c r="L5" s="6" t="inlineStr">
-        <is>
-          <t>Фланцевое</t>
-        </is>
-      </c>
-      <c r="M5" s="6" t="inlineStr">
-        <is>
-          <t>Ручное</t>
-        </is>
-      </c>
-      <c r="N5" s="6" t="inlineStr">
-        <is>
-          <t>Маховик (штурвал)</t>
-        </is>
-      </c>
-      <c r="O5" s="6" t="inlineStr">
-        <is>
-          <t>любое</t>
-        </is>
-      </c>
-      <c r="P5" s="6" t="inlineStr">
-        <is>
-          <t>Крышка — 12Х18Н10Т; седло — 12Х18Н10Т; шпиндель — 12Х18Н10Т; диск (золотник) — 12Х18Н10Т; набивка сальниковая (сальник) — ТРГ</t>
-        </is>
-      </c>
-      <c r="Q5" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>Класс герметичности по ГОСТ 9544-2015 «А» Поставка клапана с ответными фланцами 12Х18Н10Т</t>
-        </is>
-      </c>
-      <c r="S5" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="T5" s="6" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="U5" s="7" t="n"/>
-      <c r="V5" s="7" t="n"/>
-      <c r="W5" s="7" t="n"/>
-      <c r="X5" s="7" t="n"/>
-      <c r="Y5" s="7" t="n"/>
-      <c r="Z5" s="7" t="n"/>
-      <c r="AA5" s="8" t="n"/>
-      <c r="AB5" s="9">
-        <f>AA5*S5</f>
-        <v/>
-      </c>
-      <c r="AC5" s="7" t="n"/>
-      <c r="AD5" s="7" t="n"/>
-      <c r="AE5" s="7" t="n"/>
     </row>
     <row r="6" ht="60" customHeight="1">
       <c r="A6" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>1.1/4</t>
+          <t>1.1/2</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Клапан запорный15с52нж11 Ду 32 Ру 63 под приварку</t>
+          <t>Клапан запорный 15нж65нж Ду 200 Ру 16</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>ГОСТ 12.2.063-2015</t>
+          <t>ТУ 3700-001-66364836-2010</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>200</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>стандарт</t>
+          <t>Полнопроходной</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>До +400</t>
+          <t>до +6000С</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>вода пар газ и другие  рабочие среды, неагрессивные к деталям задвижки</t>
+          <t>вода, пар</t>
         </is>
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>Сталь 20</t>
+          <t>12Х18Н10Т</t>
         </is>
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>У1</t>
+          <t>УХЛ1</t>
         </is>
       </c>
       <c r="L6" s="6" t="inlineStr">
         <is>
-          <t>под приварку</t>
+          <t>Фланцевое</t>
         </is>
       </c>
       <c r="M6" s="6" t="inlineStr">
         <is>
-          <t>ручное</t>
+          <t>Ручное</t>
         </is>
       </c>
       <c r="N6" s="6" t="inlineStr">
         <is>
-          <t>рукоятка</t>
+          <t>Маховик (штурвал)</t>
         </is>
       </c>
       <c r="O6" s="6" t="inlineStr">
         <is>
-          <t>направленная</t>
+          <t>любое</t>
         </is>
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
-          <t>корпус сталь 20     золотник сталь 20х13   шпиндель сталь35 сальниковая набивка АГИ</t>
-        </is>
-      </c>
-      <c r="Q6" s="6" t="inlineStr"/>
-      <c r="R6" s="6" t="inlineStr"/>
+          <t>Крышка — 12Х18Н10Т; седло — 12Х18Н10Т; шпиндель — 12Х18Н10Т; диск (золотник) — 12Х18Н10Т; набивка сальниковая (сальник) — ТРГ</t>
+        </is>
+      </c>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>Класс герметичности по ГОСТ 9544-2015 «А» Поставка клапана с ответными фланцами 12Х18Н10Т</t>
+        </is>
+      </c>
       <c r="S6" s="5" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="T6" s="6" t="inlineStr">
         <is>
@@ -1007,26 +940,26 @@
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>1.3/41</t>
+          <t>1.1/4</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Клапан ВДХ Ду 80 Ру 10</t>
+          <t>Клапан запорный15с52нж11 Ду 32 Ру 63 под приварку</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>Класс герметичности по ГОСТ 54808"А"</t>
+          <t>ГОСТ 12.2.063-2015</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
@@ -1036,62 +969,58 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>До + 60°С</t>
+          <t>До +400</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>Вода; раствор NaOH 30%; Н2SO4 93%</t>
+          <t>вода пар газ и другие  рабочие среды, неагрессивные к деталям задвижки</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>углеродистая сталь</t>
+          <t>Сталь 20</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>У</t>
+          <t>У1</t>
         </is>
       </c>
       <c r="L7" s="6" t="inlineStr">
         <is>
-          <t>Присоединение фланцевое по ГОСТ 12815-80</t>
+          <t>под приварку</t>
         </is>
       </c>
       <c r="M7" s="6" t="inlineStr">
         <is>
-          <t>Ручное</t>
+          <t>ручное</t>
         </is>
       </c>
       <c r="N7" s="6" t="inlineStr">
         <is>
-          <t>маховик</t>
+          <t>рукоятка</t>
         </is>
       </c>
       <c r="O7" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>направленная</t>
         </is>
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
-          <t>Материал защитного покрытия-фторопласт Ф-4МБ. Мембраны-фторопласт</t>
-        </is>
-      </c>
-      <c r="Q7" s="6" t="inlineStr">
-        <is>
-          <t>строительная длина  310 мм</t>
-        </is>
-      </c>
+          <t>корпус сталь 20     золотник сталь 20х13   шпиндель сталь35 сальниковая набивка АГИ</t>
+        </is>
+      </c>
+      <c r="Q7" s="6" t="inlineStr"/>
       <c r="R7" s="6" t="inlineStr"/>
       <c r="S7" s="5" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="T7" s="6" t="inlineStr">
         <is>
@@ -1115,16 +1044,16 @@
     </row>
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>1.3/42</t>
+          <t>1.3/41</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Клапан диафрагменный химический ВДХ Ду 150 Ру 16</t>
+          <t>Клапан ВДХ Ду 80 Ру 10</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -1134,7 +1063,7 @@
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>80</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
@@ -1194,12 +1123,12 @@
       </c>
       <c r="Q8" s="6" t="inlineStr">
         <is>
-          <t>строительная длина  460 мм</t>
+          <t>строительная длина  310 мм</t>
         </is>
       </c>
       <c r="R8" s="6" t="inlineStr"/>
       <c r="S8" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T8" s="6" t="inlineStr">
         <is>
@@ -1223,16 +1152,16 @@
     </row>
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>1.3/43</t>
+          <t>1.3/42</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Клапан диафрагменный химический ВДХ Ду 50, Ру 16</t>
+          <t>Клапан диафрагменный химический ВДХ Ду 150 Ру 16</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -1242,7 +1171,7 @@
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>150</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
@@ -1257,12 +1186,12 @@
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>от -50 до +150°С</t>
+          <t>До + 60°С</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>любые жидкие реагенты и химические среды.</t>
+          <t>Вода; раствор NaOH 30%; Н2SO4 93%</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
@@ -1302,7 +1231,7 @@
       </c>
       <c r="Q9" s="6" t="inlineStr">
         <is>
-          <t>строительная длина  210 мм,</t>
+          <t>строительная длина  460 мм</t>
         </is>
       </c>
       <c r="R9" s="6" t="inlineStr"/>
@@ -1331,16 +1260,16 @@
     </row>
     <row r="10" ht="60" customHeight="1">
       <c r="A10" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>1.3/44</t>
+          <t>1.3/43</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Клапан диафрагменный химический ВДХ Ду 80 Ру 16</t>
+          <t>Клапан диафрагменный химический ВДХ Ду 50, Ру 16</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -1350,7 +1279,7 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
@@ -1410,12 +1339,12 @@
       </c>
       <c r="Q10" s="6" t="inlineStr">
         <is>
-          <t>строительная длина  310 мм,</t>
+          <t>строительная длина  210 мм,</t>
         </is>
       </c>
       <c r="R10" s="6" t="inlineStr"/>
       <c r="S10" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T10" s="6" t="inlineStr">
         <is>
@@ -1439,26 +1368,26 @@
     </row>
     <row r="11" ht="60" customHeight="1">
       <c r="A11" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>1.3/63</t>
+          <t>1.3/44</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Клапан запорный 15с52нж11 Ду 20 Ру 63 под приварку</t>
+          <t>Клапан диафрагменный химический ВДХ Ду 80 Ру 16</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>ГОСТ 9697-87</t>
+          <t>Класс герметичности по ГОСТ 54808"А"</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>80</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
@@ -1468,63 +1397,62 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>до + 425°С</t>
+          <t>от -50 до +150°С</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>вода, слабоагрессивные жидкие среды</t>
+          <t>любые жидкие реагенты и химические среды.</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>Сталь 25 Л</t>
+          <t>углеродистая сталь</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>У1</t>
+          <t>У</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
         <is>
-          <t>под приварку</t>
+          <t>Присоединение фланцевое по ГОСТ 12815-80</t>
         </is>
       </c>
       <c r="M11" s="6" t="inlineStr">
         <is>
-          <t>ручное</t>
+          <t>Ручное</t>
         </is>
       </c>
       <c r="N11" s="6" t="inlineStr">
         <is>
-          <t>маховик, рукоятка</t>
+          <t>маховик</t>
         </is>
       </c>
       <c r="O11" s="6" t="inlineStr">
         <is>
-          <t>любом рабочем положении</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
-          <t>Материал корпуса, диска, крышки: сталь 25
-Материал седла, шпинделя: нержавеющая сталь</t>
+          <t>Материал защитного покрытия-фторопласт Ф-4МБ. Мембраны-фторопласт</t>
         </is>
       </c>
       <c r="Q11" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>строительная длина  310 мм,</t>
         </is>
       </c>
       <c r="R11" s="6" t="inlineStr"/>
       <c r="S11" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T11" s="6" t="inlineStr">
         <is>
@@ -1548,21 +1476,21 @@
     </row>
     <row r="12" ht="60" customHeight="1">
       <c r="A12" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>1.3/67</t>
+          <t>1.3/63</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Клапан запорный 15ч93эм Ду 20 Ру 16</t>
+          <t>Клапан запорный 15с52нж11 Ду 20 Ру 63 под приварку</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>ТУ 26-07-1051-84</t>
+          <t>ГОСТ 9697-87</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -1577,32 +1505,32 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>От -15°С до +120°С</t>
+          <t>до + 425°С</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>Агрессивная</t>
+          <t>вода, слабоагрессивные жидкие среды</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>Серый чугун СЧ18</t>
+          <t>Сталь 25 Л</t>
         </is>
       </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
-          <t>УХЛ4</t>
+          <t>У1</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr">
         <is>
-          <t>фланец-фланец</t>
+          <t>под приварку</t>
         </is>
       </c>
       <c r="M12" s="6" t="inlineStr">
@@ -1612,31 +1540,28 @@
       </c>
       <c r="N12" s="6" t="inlineStr">
         <is>
-          <t>маховик</t>
+          <t>маховик, рукоятка</t>
         </is>
       </c>
       <c r="O12" s="6" t="inlineStr">
         <is>
-          <t>любое</t>
+          <t>любом рабочем положении</t>
         </is>
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
-          <t>Корпус: чугун.
-Крышка: чугун.
-Шпиндель: сталь.
-Крестовина: чугун.
-Диафрагма: фторопласт-4.</t>
+          <t>Материал корпуса, диска, крышки: сталь 25
+Материал седла, шпинделя: нержавеющая сталь</t>
         </is>
       </c>
       <c r="Q12" s="6" t="inlineStr">
         <is>
-          <t>L-150мм, Н-146мм</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R12" s="6" t="inlineStr"/>
       <c r="S12" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T12" s="6" t="inlineStr">
         <is>
@@ -1660,26 +1585,26 @@
     </row>
     <row r="13" ht="60" customHeight="1">
       <c r="A13" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>1.6/20</t>
+          <t>1.3/67</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Клапан запорный 15кч12пМ Ду 25 Ру 25</t>
+          <t>Клапан запорный 15ч93эм Ду 20 Ру 16</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>ТУ 3732-001-00218137-94</t>
+          <t>ТУ 26-07-1051-84</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -1689,42 +1614,42 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>от -40 до +150</t>
+          <t>От -15°С до +120°С</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>Хладон, аммиак, вода, пар</t>
+          <t>Агрессивная</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>ковкий чугун КЧ 30-6</t>
+          <t>Серый чугун СЧ18</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>УХЛ4 Температура окружающей среды от - 30 до +50</t>
+          <t>УХЛ4</t>
         </is>
       </c>
       <c r="L13" s="6" t="inlineStr">
         <is>
-          <t>фланцевый</t>
+          <t>фланец-фланец</t>
         </is>
       </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
-          <t>ручной (маховик)</t>
+          <t>ручное</t>
         </is>
       </c>
       <c r="N13" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>маховик</t>
         </is>
       </c>
       <c r="O13" s="6" t="inlineStr">
@@ -1734,22 +1659,21 @@
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
-          <t>Золотник, шпиндель - сталь;
-Уплотнение - Фторопласт-4</t>
+          <t>Корпус: чугун.
+Крышка: чугун.
+Шпиндель: сталь.
+Крестовина: чугун.
+Диафрагма: фторопласт-4.</t>
         </is>
       </c>
       <c r="Q13" s="6" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>L-150мм, Н-146мм</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr"/>
       <c r="S13" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T13" s="6" t="inlineStr">
         <is>
@@ -1772,44 +1696,157 @@
       <c r="AE13" s="7" t="n"/>
     </row>
     <row r="14" ht="60" customHeight="1">
-      <c r="A14" s="10" t="inlineStr"/>
-      <c r="B14" s="10" t="inlineStr"/>
-      <c r="C14" s="10" t="inlineStr"/>
-      <c r="D14" s="10" t="inlineStr"/>
-      <c r="E14" s="10" t="inlineStr"/>
-      <c r="F14" s="10" t="inlineStr"/>
-      <c r="G14" s="10" t="inlineStr"/>
-      <c r="H14" s="10" t="inlineStr"/>
-      <c r="I14" s="10" t="inlineStr"/>
-      <c r="J14" s="10" t="inlineStr"/>
-      <c r="K14" s="10" t="inlineStr"/>
-      <c r="L14" s="10" t="inlineStr"/>
-      <c r="M14" s="10" t="inlineStr"/>
-      <c r="N14" s="10" t="inlineStr"/>
-      <c r="O14" s="10" t="inlineStr"/>
-      <c r="P14" s="10" t="inlineStr"/>
-      <c r="Q14" s="10" t="inlineStr"/>
-      <c r="R14" s="10" t="inlineStr"/>
-      <c r="S14" s="10" t="inlineStr"/>
-      <c r="T14" s="10" t="inlineStr"/>
-      <c r="U14" s="10" t="inlineStr"/>
-      <c r="V14" s="10" t="inlineStr"/>
-      <c r="W14" s="10" t="inlineStr"/>
-      <c r="X14" s="10" t="inlineStr"/>
-      <c r="Y14" s="10" t="inlineStr"/>
-      <c r="Z14" s="10" t="inlineStr"/>
-      <c r="AA14" s="10" t="inlineStr">
+      <c r="A14" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>1.6/20</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Клапан запорный 15кч12пМ Ду 25 Ру 25</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>ТУ 3732-001-00218137-94</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>от -40 до +150</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>Хладон, аммиак, вода, пар</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>ковкий чугун КЧ 30-6</t>
+        </is>
+      </c>
+      <c r="K14" s="6" t="inlineStr">
+        <is>
+          <t>УХЛ4 Температура окружающей среды от - 30 до +50</t>
+        </is>
+      </c>
+      <c r="L14" s="6" t="inlineStr">
+        <is>
+          <t>фланцевый</t>
+        </is>
+      </c>
+      <c r="M14" s="6" t="inlineStr">
+        <is>
+          <t>ручной (маховик)</t>
+        </is>
+      </c>
+      <c r="N14" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O14" s="6" t="inlineStr">
+        <is>
+          <t>любое</t>
+        </is>
+      </c>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>Золотник, шпиндель - сталь;
+Уплотнение - Фторопласт-4</t>
+        </is>
+      </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="U14" s="7" t="n"/>
+      <c r="V14" s="7" t="n"/>
+      <c r="W14" s="7" t="n"/>
+      <c r="X14" s="7" t="n"/>
+      <c r="Y14" s="7" t="n"/>
+      <c r="Z14" s="7" t="n"/>
+      <c r="AA14" s="8" t="n"/>
+      <c r="AB14" s="9">
+        <f>AA14*S14</f>
+        <v/>
+      </c>
+      <c r="AC14" s="7" t="n"/>
+      <c r="AD14" s="7" t="n"/>
+      <c r="AE14" s="7" t="n"/>
+    </row>
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" s="10" t="inlineStr"/>
+      <c r="B15" s="10" t="inlineStr"/>
+      <c r="C15" s="10" t="inlineStr"/>
+      <c r="D15" s="10" t="inlineStr"/>
+      <c r="E15" s="10" t="inlineStr"/>
+      <c r="F15" s="10" t="inlineStr"/>
+      <c r="G15" s="10" t="inlineStr"/>
+      <c r="H15" s="10" t="inlineStr"/>
+      <c r="I15" s="10" t="inlineStr"/>
+      <c r="J15" s="10" t="inlineStr"/>
+      <c r="K15" s="10" t="inlineStr"/>
+      <c r="L15" s="10" t="inlineStr"/>
+      <c r="M15" s="10" t="inlineStr"/>
+      <c r="N15" s="10" t="inlineStr"/>
+      <c r="O15" s="10" t="inlineStr"/>
+      <c r="P15" s="10" t="inlineStr"/>
+      <c r="Q15" s="10" t="inlineStr"/>
+      <c r="R15" s="10" t="inlineStr"/>
+      <c r="S15" s="10" t="inlineStr"/>
+      <c r="T15" s="10" t="inlineStr"/>
+      <c r="U15" s="10" t="inlineStr"/>
+      <c r="V15" s="10" t="inlineStr"/>
+      <c r="W15" s="10" t="inlineStr"/>
+      <c r="X15" s="10" t="inlineStr"/>
+      <c r="Y15" s="10" t="inlineStr"/>
+      <c r="Z15" s="10" t="inlineStr"/>
+      <c r="AA15" s="10" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="AB14" s="11">
-        <f>SUM(AB5:AB13)</f>
+      <c r="AB15" s="11">
+        <f>SUM(AB6:AB14)</f>
         <v/>
       </c>
-      <c r="AC14" s="2" t="n"/>
-      <c r="AD14" s="2" t="n"/>
-      <c r="AE14" s="2" t="n"/>
+      <c r="AC15" s="2" t="n"/>
+      <c r="AD15" s="2" t="n"/>
+      <c r="AE15" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/KAMCHATKA_ZAPOLNENIE/05_АО_Благовещенский_арматурный_завод.xlsx
+++ b/KAMCHATKA_ZAPOLNENIE/05_АО_Благовещенский_арматурный_завод.xlsx
@@ -85,7 +85,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -107,6 +107,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -485,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AE15"/>
+  <dimension ref="A1:AE26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -832,17 +835,17 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>1.1/2</t>
+          <t>1.1/1</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Клапан запорный 15нж65нж Ду 200 Ру 16</t>
+          <t>Клапан предохранительный 17лс17нж Ду 200-300  Ру 16-6 полноподъемный пружинный фланцевый</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>ТУ 3700-001-66364836-2010</t>
+          <t>ТУ 3742-001-09212465-2016; ГОСТ 5761-2005, ГОСТ 9544-2015, ГОСТ 16587-71, ГОСТ 356-80</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -852,7 +855,7 @@
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>Полнопроходной</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
@@ -862,61 +865,57 @@
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>до +6000С</t>
+          <t>От -40 °C до +225°С</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>вода, пар</t>
+          <t>Жидкая и газообразная в которой скорость коррозии сталей не превышает 0,1 мм/год</t>
         </is>
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>12Х18Н10Т</t>
+          <t>Корпус — сталь 20ГЛ ГОСТ 977-88;  Крышка — ст.20</t>
         </is>
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>УХЛ1</t>
+          <t>У1</t>
         </is>
       </c>
       <c r="L6" s="6" t="inlineStr">
         <is>
-          <t>Фланцевое</t>
+          <t>фланец-фланец</t>
         </is>
       </c>
       <c r="M6" s="6" t="inlineStr">
         <is>
-          <t>Ручное</t>
+          <t>автоматическое/ручное</t>
         </is>
       </c>
       <c r="N6" s="6" t="inlineStr">
         <is>
-          <t>Маховик (штурвал)</t>
+          <t>Рукоятка</t>
         </is>
       </c>
       <c r="O6" s="6" t="inlineStr">
         <is>
-          <t>любое</t>
+          <t>вертикально, колпаком вверх с подачей среды под золотник</t>
         </is>
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
-          <t>Крышка — 12Х18Н10Т; седло — 12Х18Н10Т; шпиндель — 12Х18Н10Т; диск (золотник) — 12Х18Н10Т; набивка сальниковая (сальник) — ТРГ</t>
+          <t>Седло — ст.20Х13; Золотник — ст.30Х13, Шток — ст.20Х13, Пружина — 50ХФА или 51ХФА. Площадь седла F - 15836 мм2;</t>
         </is>
       </c>
       <c r="Q6" s="6" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>Класс герметичности по ГОСТ 9544-2015 «А» Поставка клапана с ответными фланцами 12Х18Н10Т</t>
-        </is>
-      </c>
+          <t>Строительная длина L/L1 мм — 280/320</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr"/>
       <c r="S6" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T6" s="6" t="inlineStr">
         <is>
@@ -924,13 +923,29 @@
         </is>
       </c>
       <c r="U6" s="7" t="n"/>
-      <c r="V6" s="7" t="n"/>
-      <c r="W6" s="7" t="n"/>
-      <c r="X6" s="7" t="n"/>
-      <c r="Y6" s="7" t="n"/>
+      <c r="V6" s="8" t="inlineStr">
+        <is>
+          <t>АО «Благовещенский арматурный завод»</t>
+        </is>
+      </c>
+      <c r="W6" s="8" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="X6" s="8" t="inlineStr">
+        <is>
+          <t>10329690</t>
+        </is>
+      </c>
+      <c r="Y6" s="8" t="inlineStr">
+        <is>
+          <t>16.09.2030</t>
+        </is>
+      </c>
       <c r="Z6" s="7" t="n"/>
-      <c r="AA6" s="8" t="n"/>
-      <c r="AB6" s="9">
+      <c r="AA6" s="9" t="n"/>
+      <c r="AB6" s="10">
         <f>AA6*S6</f>
         <v/>
       </c>
@@ -944,83 +959,91 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>1.1/4</t>
+          <t>1.1/2</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Клапан запорный15с52нж11 Ду 32 Ру 63 под приварку</t>
+          <t>Клапан запорный 15нж65нж Ду 200 Ру 16</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>ГОСТ 12.2.063-2015</t>
+          <t>ТУ 3700-001-66364836-2010</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>200</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>стандарт</t>
+          <t>Полнопроходной</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>До +400</t>
+          <t>до +6000С</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>вода пар газ и другие  рабочие среды, неагрессивные к деталям задвижки</t>
+          <t>вода, пар</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>Сталь 20</t>
+          <t>12Х18Н10Т</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>У1</t>
+          <t>УХЛ1</t>
         </is>
       </c>
       <c r="L7" s="6" t="inlineStr">
         <is>
-          <t>под приварку</t>
+          <t>Фланцевое</t>
         </is>
       </c>
       <c r="M7" s="6" t="inlineStr">
         <is>
-          <t>ручное</t>
+          <t>Ручное</t>
         </is>
       </c>
       <c r="N7" s="6" t="inlineStr">
         <is>
-          <t>рукоятка</t>
+          <t>Маховик (штурвал)</t>
         </is>
       </c>
       <c r="O7" s="6" t="inlineStr">
         <is>
-          <t>направленная</t>
+          <t>любое</t>
         </is>
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
-          <t>корпус сталь 20     золотник сталь 20х13   шпиндель сталь35 сальниковая набивка АГИ</t>
-        </is>
-      </c>
-      <c r="Q7" s="6" t="inlineStr"/>
-      <c r="R7" s="6" t="inlineStr"/>
+          <t>Крышка — 12Х18Н10Т; седло — 12Х18Н10Т; шпиндель — 12Х18Н10Т; диск (золотник) — 12Х18Н10Т; набивка сальниковая (сальник) — ТРГ</t>
+        </is>
+      </c>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>Класс герметичности по ГОСТ 9544-2015 «А» Поставка клапана с ответными фланцами 12Х18Н10Т</t>
+        </is>
+      </c>
       <c r="S7" s="5" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="T7" s="6" t="inlineStr">
         <is>
@@ -1033,8 +1056,8 @@
       <c r="X7" s="7" t="n"/>
       <c r="Y7" s="7" t="n"/>
       <c r="Z7" s="7" t="n"/>
-      <c r="AA7" s="8" t="n"/>
-      <c r="AB7" s="9">
+      <c r="AA7" s="9" t="n"/>
+      <c r="AB7" s="10">
         <f>AA7*S7</f>
         <v/>
       </c>
@@ -1048,22 +1071,22 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>1.3/41</t>
+          <t>1.1/4</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Клапан ВДХ Ду 80 Ру 10</t>
+          <t>Клапан запорный15с52нж11 Ду 32 Ру 63 под приварку</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>Класс герметичности по ГОСТ 54808"А"</t>
+          <t>ГОСТ 12.2.063-2015</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
@@ -1073,62 +1096,58 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>До + 60°С</t>
+          <t>До +400</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>Вода; раствор NaOH 30%; Н2SO4 93%</t>
+          <t>вода пар газ и другие  рабочие среды, неагрессивные к деталям задвижки</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>углеродистая сталь</t>
+          <t>Сталь 20</t>
         </is>
       </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
-          <t>У</t>
+          <t>У1</t>
         </is>
       </c>
       <c r="L8" s="6" t="inlineStr">
         <is>
-          <t>Присоединение фланцевое по ГОСТ 12815-80</t>
+          <t>под приварку</t>
         </is>
       </c>
       <c r="M8" s="6" t="inlineStr">
         <is>
-          <t>Ручное</t>
+          <t>ручное</t>
         </is>
       </c>
       <c r="N8" s="6" t="inlineStr">
         <is>
-          <t>маховик</t>
+          <t>рукоятка</t>
         </is>
       </c>
       <c r="O8" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>направленная</t>
         </is>
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
-          <t>Материал защитного покрытия-фторопласт Ф-4МБ. Мембраны-фторопласт</t>
-        </is>
-      </c>
-      <c r="Q8" s="6" t="inlineStr">
-        <is>
-          <t>строительная длина  310 мм</t>
-        </is>
-      </c>
+          <t>корпус сталь 20     золотник сталь 20х13   шпиндель сталь35 сальниковая набивка АГИ</t>
+        </is>
+      </c>
+      <c r="Q8" s="6" t="inlineStr"/>
       <c r="R8" s="6" t="inlineStr"/>
       <c r="S8" s="5" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="T8" s="6" t="inlineStr">
         <is>
@@ -1141,8 +1160,8 @@
       <c r="X8" s="7" t="n"/>
       <c r="Y8" s="7" t="n"/>
       <c r="Z8" s="7" t="n"/>
-      <c r="AA8" s="8" t="n"/>
-      <c r="AB8" s="9">
+      <c r="AA8" s="9" t="n"/>
+      <c r="AB8" s="10">
         <f>AA8*S8</f>
         <v/>
       </c>
@@ -1156,47 +1175,39 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>1.3/42</t>
+          <t>1.3/14</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Клапан диафрагменный химический ВДХ Ду 150 Ру 16</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>Класс герметичности по ГОСТ 54808"А"</t>
-        </is>
-      </c>
+          <t>Клапан обратный 19с53нж Ду 80 Ру 40</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr"/>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>стандарт</t>
-        </is>
-      </c>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr"/>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>До + 60°С</t>
+          <t>От -29 до    +425С</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>Вода; раствор NaOH 30%; Н2SO4 93%</t>
+          <t>Вода</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>углеродистая сталь</t>
+          <t>Углеродистая сталь</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
@@ -1206,37 +1217,21 @@
       </c>
       <c r="L9" s="6" t="inlineStr">
         <is>
-          <t>Присоединение фланцевое по ГОСТ 12815-80</t>
-        </is>
-      </c>
-      <c r="M9" s="6" t="inlineStr">
-        <is>
-          <t>Ручное</t>
-        </is>
-      </c>
-      <c r="N9" s="6" t="inlineStr">
-        <is>
-          <t>маховик</t>
-        </is>
-      </c>
-      <c r="O9" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Фланцевое</t>
+        </is>
+      </c>
+      <c r="M9" s="6" t="inlineStr"/>
+      <c r="N9" s="6" t="inlineStr"/>
+      <c r="O9" s="6" t="inlineStr"/>
       <c r="P9" s="6" t="inlineStr">
         <is>
-          <t>Материал защитного покрытия-фторопласт Ф-4МБ. Мембраны-фторопласт</t>
-        </is>
-      </c>
-      <c r="Q9" s="6" t="inlineStr">
-        <is>
-          <t>строительная длина  460 мм</t>
-        </is>
-      </c>
+          <t>Материа запорного органа - Сталь (A216 WCB + 13Cr), Тип уплотнения - Графит+нержавеющая сталь</t>
+        </is>
+      </c>
+      <c r="Q9" s="6" t="inlineStr"/>
       <c r="R9" s="6" t="inlineStr"/>
       <c r="S9" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T9" s="6" t="inlineStr">
         <is>
@@ -1244,13 +1239,29 @@
         </is>
       </c>
       <c r="U9" s="7" t="n"/>
-      <c r="V9" s="7" t="n"/>
-      <c r="W9" s="7" t="n"/>
-      <c r="X9" s="7" t="n"/>
-      <c r="Y9" s="7" t="n"/>
+      <c r="V9" s="8" t="inlineStr">
+        <is>
+          <t>АО «Благовещенский арматурный завод»</t>
+        </is>
+      </c>
+      <c r="W9" s="8" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="X9" s="8" t="inlineStr">
+        <is>
+          <t>10329682</t>
+        </is>
+      </c>
+      <c r="Y9" s="8" t="inlineStr">
+        <is>
+          <t>16.09.2030</t>
+        </is>
+      </c>
       <c r="Z9" s="7" t="n"/>
-      <c r="AA9" s="8" t="n"/>
-      <c r="AB9" s="9">
+      <c r="AA9" s="9" t="n"/>
+      <c r="AB9" s="10">
         <f>AA9*S9</f>
         <v/>
       </c>
@@ -1264,47 +1275,39 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>1.3/43</t>
+          <t>1.3/15</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Клапан диафрагменный химический ВДХ Ду 50, Ру 16</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>Класс герметичности по ГОСТ 54808"А"</t>
-        </is>
-      </c>
+          <t>Клапан обратный 19с53нж Ду 150 Ру 40</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr"/>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>стандарт</t>
-        </is>
-      </c>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr"/>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>от -50 до +150°С</t>
+          <t>От -29 до    +425С</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>любые жидкие реагенты и химические среды.</t>
+          <t>Вода</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>углеродистая сталь</t>
+          <t>Углеродистая сталь</t>
         </is>
       </c>
       <c r="K10" s="6" t="inlineStr">
@@ -1314,37 +1317,21 @@
       </c>
       <c r="L10" s="6" t="inlineStr">
         <is>
-          <t>Присоединение фланцевое по ГОСТ 12815-80</t>
-        </is>
-      </c>
-      <c r="M10" s="6" t="inlineStr">
-        <is>
-          <t>Ручное</t>
-        </is>
-      </c>
-      <c r="N10" s="6" t="inlineStr">
-        <is>
-          <t>маховик</t>
-        </is>
-      </c>
-      <c r="O10" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Фланцевое</t>
+        </is>
+      </c>
+      <c r="M10" s="6" t="inlineStr"/>
+      <c r="N10" s="6" t="inlineStr"/>
+      <c r="O10" s="6" t="inlineStr"/>
       <c r="P10" s="6" t="inlineStr">
         <is>
-          <t>Материал защитного покрытия-фторопласт Ф-4МБ. Мембраны-фторопласт</t>
-        </is>
-      </c>
-      <c r="Q10" s="6" t="inlineStr">
-        <is>
-          <t>строительная длина  210 мм,</t>
-        </is>
-      </c>
+          <t>Материа запорного органа - Сталь (A216 WCB + 13Cr), Тип уплотнения - Графит+нержавеющая сталь</t>
+        </is>
+      </c>
+      <c r="Q10" s="6" t="inlineStr"/>
       <c r="R10" s="6" t="inlineStr"/>
       <c r="S10" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T10" s="6" t="inlineStr">
         <is>
@@ -1352,13 +1339,29 @@
         </is>
       </c>
       <c r="U10" s="7" t="n"/>
-      <c r="V10" s="7" t="n"/>
-      <c r="W10" s="7" t="n"/>
-      <c r="X10" s="7" t="n"/>
-      <c r="Y10" s="7" t="n"/>
+      <c r="V10" s="8" t="inlineStr">
+        <is>
+          <t>АО «Благовещенский арматурный завод»</t>
+        </is>
+      </c>
+      <c r="W10" s="8" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="X10" s="8" t="inlineStr">
+        <is>
+          <t>10329682</t>
+        </is>
+      </c>
+      <c r="Y10" s="8" t="inlineStr">
+        <is>
+          <t>16.09.2030</t>
+        </is>
+      </c>
       <c r="Z10" s="7" t="n"/>
-      <c r="AA10" s="8" t="n"/>
-      <c r="AB10" s="9">
+      <c r="AA10" s="9" t="n"/>
+      <c r="AB10" s="10">
         <f>AA10*S10</f>
         <v/>
       </c>
@@ -1372,87 +1375,59 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>1.3/44</t>
+          <t>1.3/21</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Клапан диафрагменный химический ВДХ Ду 80 Ру 16</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>Класс герметичности по ГОСТ 54808"А"</t>
-        </is>
-      </c>
+          <t>Клапан обратный фланцевый Ду 50 Ру 40</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr"/>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>стандарт</t>
-        </is>
-      </c>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr"/>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>от -50 до +150°С</t>
+          <t>От -29 до    +425С</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>любые жидкие реагенты и химические среды.</t>
+          <t>Вода</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>углеродистая сталь</t>
-        </is>
-      </c>
-      <c r="K11" s="6" t="inlineStr">
-        <is>
-          <t>У</t>
-        </is>
-      </c>
+          <t>Углеродистая сталь</t>
+        </is>
+      </c>
+      <c r="K11" s="6" t="inlineStr"/>
       <c r="L11" s="6" t="inlineStr">
         <is>
-          <t>Присоединение фланцевое по ГОСТ 12815-80</t>
-        </is>
-      </c>
-      <c r="M11" s="6" t="inlineStr">
-        <is>
-          <t>Ручное</t>
-        </is>
-      </c>
-      <c r="N11" s="6" t="inlineStr">
-        <is>
-          <t>маховик</t>
-        </is>
-      </c>
-      <c r="O11" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Фланцевое</t>
+        </is>
+      </c>
+      <c r="M11" s="6" t="inlineStr"/>
+      <c r="N11" s="6" t="inlineStr"/>
+      <c r="O11" s="6" t="inlineStr"/>
       <c r="P11" s="6" t="inlineStr">
         <is>
-          <t>Материал защитного покрытия-фторопласт Ф-4МБ. Мембраны-фторопласт</t>
-        </is>
-      </c>
-      <c r="Q11" s="6" t="inlineStr">
-        <is>
-          <t>строительная длина  310 мм,</t>
-        </is>
-      </c>
+          <t>Материа запорного органа - Сталь (A216 WCB + 13Cr), Тип уплотнения - Графит+нержавеющая сталь</t>
+        </is>
+      </c>
+      <c r="Q11" s="6" t="inlineStr"/>
       <c r="R11" s="6" t="inlineStr"/>
       <c r="S11" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T11" s="6" t="inlineStr">
         <is>
@@ -1460,13 +1435,29 @@
         </is>
       </c>
       <c r="U11" s="7" t="n"/>
-      <c r="V11" s="7" t="n"/>
-      <c r="W11" s="7" t="n"/>
-      <c r="X11" s="7" t="n"/>
-      <c r="Y11" s="7" t="n"/>
+      <c r="V11" s="8" t="inlineStr">
+        <is>
+          <t>АО «Благовещенский арматурный завод»</t>
+        </is>
+      </c>
+      <c r="W11" s="8" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="X11" s="8" t="inlineStr">
+        <is>
+          <t>10329682</t>
+        </is>
+      </c>
+      <c r="Y11" s="8" t="inlineStr">
+        <is>
+          <t>16.09.2030</t>
+        </is>
+      </c>
       <c r="Z11" s="7" t="n"/>
-      <c r="AA11" s="8" t="n"/>
-      <c r="AB11" s="9">
+      <c r="AA11" s="9" t="n"/>
+      <c r="AB11" s="10">
         <f>AA11*S11</f>
         <v/>
       </c>
@@ -1480,12 +1471,12 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>1.3/63</t>
+          <t>1.3/26</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Клапан запорный 15с52нж11 Ду 20 Ру 63 под приварку</t>
+          <t>Клапан обратный 19нж76нж Ду 100 Ру 16</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -1495,7 +1486,7 @@
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -1505,32 +1496,32 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>до + 425°С</t>
+          <t>от -60 до +600°С</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>вода, слабоагрессивные жидкие среды</t>
+          <t>агрессивные жидкие среды</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>Сталь 25 Л</t>
+          <t>12Х18Н9ТЛ</t>
         </is>
       </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
-          <t>У1</t>
+          <t>УХЛ1</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr">
         <is>
-          <t>под приварку</t>
+          <t>фланец-фланец</t>
         </is>
       </c>
       <c r="M12" s="6" t="inlineStr">
@@ -1540,28 +1531,23 @@
       </c>
       <c r="N12" s="6" t="inlineStr">
         <is>
-          <t>маховик, рукоятка</t>
+          <t>штурвал</t>
         </is>
       </c>
       <c r="O12" s="6" t="inlineStr">
         <is>
-          <t>любом рабочем положении</t>
+          <t>Монтаж вентиля односторонний по маркировке на корпусе управляющим органом вверх, допускается отклонение на горизонтальном трубопроводе на 45º в любую сторону.</t>
         </is>
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
-          <t>Материал корпуса, диска, крышки: сталь 25
-Материал седла, шпинделя: нержавеющая сталь</t>
-        </is>
-      </c>
-      <c r="Q12" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Материал изделия (корпус, крышка): сталь 12Х18Н9ТЛ;</t>
+        </is>
+      </c>
+      <c r="Q12" s="6" t="inlineStr"/>
       <c r="R12" s="6" t="inlineStr"/>
       <c r="S12" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T12" s="6" t="inlineStr">
         <is>
@@ -1569,13 +1555,29 @@
         </is>
       </c>
       <c r="U12" s="7" t="n"/>
-      <c r="V12" s="7" t="n"/>
-      <c r="W12" s="7" t="n"/>
-      <c r="X12" s="7" t="n"/>
-      <c r="Y12" s="7" t="n"/>
+      <c r="V12" s="8" t="inlineStr">
+        <is>
+          <t>АО «Благовещенский арматурный завод»</t>
+        </is>
+      </c>
+      <c r="W12" s="8" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="X12" s="8" t="inlineStr">
+        <is>
+          <t>10329682</t>
+        </is>
+      </c>
+      <c r="Y12" s="8" t="inlineStr">
+        <is>
+          <t>16.09.2030</t>
+        </is>
+      </c>
       <c r="Z12" s="7" t="n"/>
-      <c r="AA12" s="8" t="n"/>
-      <c r="AB12" s="9">
+      <c r="AA12" s="9" t="n"/>
+      <c r="AB12" s="10">
         <f>AA12*S12</f>
         <v/>
       </c>
@@ -1589,22 +1591,22 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>1.3/67</t>
+          <t>1.3/27</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Клапан запорный 15ч93эм Ду 20 Ру 16</t>
+          <t>Клапан обратный 19с76нж Ду 80 Ру 16</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>ТУ 26-07-1051-84</t>
+          <t>ГОСТ 33423-2015</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>80</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -1619,22 +1621,22 @@
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>От -15°С до +120°С</t>
+          <t>до +425°С</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>Агрессивная</t>
+          <t>Вода</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>Серый чугун СЧ18</t>
+          <t>Сталь 25Л</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>УХЛ4</t>
+          <t>У1</t>
         </is>
       </c>
       <c r="L13" s="6" t="inlineStr">
@@ -1644,14 +1646,10 @@
       </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
-          <t>ручное</t>
-        </is>
-      </c>
-      <c r="N13" s="6" t="inlineStr">
-        <is>
-          <t>маховик</t>
-        </is>
-      </c>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="N13" s="6" t="inlineStr"/>
       <c r="O13" s="6" t="inlineStr">
         <is>
           <t>любое</t>
@@ -1659,21 +1657,13 @@
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
-          <t>Корпус: чугун.
-Крышка: чугун.
-Шпиндель: сталь.
-Крестовина: чугун.
-Диафрагма: фторопласт-4.</t>
-        </is>
-      </c>
-      <c r="Q13" s="6" t="inlineStr">
-        <is>
-          <t>L-150мм, Н-146мм</t>
-        </is>
-      </c>
+          <t>Крышка  Ст.20 Захлопка  Ст. 20 Серьга  Ст.20Л-30Л Кронштейн, ось  Ст. 20Х13 Уплотнение затвора  Наплавленная коррозионно-стойкая сталь 08Х20Н9Г7Т</t>
+        </is>
+      </c>
+      <c r="Q13" s="6" t="inlineStr"/>
       <c r="R13" s="6" t="inlineStr"/>
       <c r="S13" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T13" s="6" t="inlineStr">
         <is>
@@ -1681,13 +1671,29 @@
         </is>
       </c>
       <c r="U13" s="7" t="n"/>
-      <c r="V13" s="7" t="n"/>
-      <c r="W13" s="7" t="n"/>
-      <c r="X13" s="7" t="n"/>
-      <c r="Y13" s="7" t="n"/>
+      <c r="V13" s="8" t="inlineStr">
+        <is>
+          <t>АО «Благовещенский арматурный завод»</t>
+        </is>
+      </c>
+      <c r="W13" s="8" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="X13" s="8" t="inlineStr">
+        <is>
+          <t>10329682</t>
+        </is>
+      </c>
+      <c r="Y13" s="8" t="inlineStr">
+        <is>
+          <t>16.09.2030</t>
+        </is>
+      </c>
       <c r="Z13" s="7" t="n"/>
-      <c r="AA13" s="8" t="n"/>
-      <c r="AB13" s="9">
+      <c r="AA13" s="9" t="n"/>
+      <c r="AB13" s="10">
         <f>AA13*S13</f>
         <v/>
       </c>
@@ -1701,22 +1707,22 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>1.6/20</t>
+          <t>1.3/28</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Клапан запорный 15кч12пМ Ду 25 Ру 25</t>
+          <t>Клапан обратный 19с76нж Ду 100 Ру 16</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>ТУ 3732-001-00218137-94</t>
+          <t>ГОСТ 33423-2015</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -1726,67 +1732,50 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>от -40 до +150</t>
+          <t>- до 425 ºC</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>Хладон, аммиак, вода, пар</t>
+          <t>вода</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>ковкий чугун КЧ 30-6</t>
+          <t>сталь 25Л, 20, 20Х13</t>
         </is>
       </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
-          <t>УХЛ4 Температура окружающей среды от - 30 до +50</t>
+          <t>У1</t>
         </is>
       </c>
       <c r="L14" s="6" t="inlineStr">
         <is>
-          <t>фланцевый</t>
+          <t>Фланец-фланец</t>
         </is>
       </c>
       <c r="M14" s="6" t="inlineStr">
         <is>
-          <t>ручной (маховик)</t>
-        </is>
-      </c>
-      <c r="N14" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="N14" s="6" t="inlineStr"/>
       <c r="O14" s="6" t="inlineStr">
         <is>
-          <t>любое</t>
-        </is>
-      </c>
-      <c r="P14" s="6" t="inlineStr">
-        <is>
-          <t>Золотник, шпиндель - сталь;
-Уплотнение - Фторопласт-4</t>
-        </is>
-      </c>
-      <c r="Q14" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>на горизонтальном трубопроводе крышкой вверх; на вертикальном – входным патрубком вверх</t>
+        </is>
+      </c>
+      <c r="P14" s="6" t="inlineStr"/>
+      <c r="Q14" s="6" t="inlineStr"/>
+      <c r="R14" s="6" t="inlineStr"/>
       <c r="S14" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T14" s="6" t="inlineStr">
         <is>
@@ -1794,13 +1783,29 @@
         </is>
       </c>
       <c r="U14" s="7" t="n"/>
-      <c r="V14" s="7" t="n"/>
-      <c r="W14" s="7" t="n"/>
-      <c r="X14" s="7" t="n"/>
-      <c r="Y14" s="7" t="n"/>
+      <c r="V14" s="8" t="inlineStr">
+        <is>
+          <t>АО «Благовещенский арматурный завод»</t>
+        </is>
+      </c>
+      <c r="W14" s="8" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="X14" s="8" t="inlineStr">
+        <is>
+          <t>10329682</t>
+        </is>
+      </c>
+      <c r="Y14" s="8" t="inlineStr">
+        <is>
+          <t>16.09.2030</t>
+        </is>
+      </c>
       <c r="Z14" s="7" t="n"/>
-      <c r="AA14" s="8" t="n"/>
-      <c r="AB14" s="9">
+      <c r="AA14" s="9" t="n"/>
+      <c r="AB14" s="10">
         <f>AA14*S14</f>
         <v/>
       </c>
@@ -1809,44 +1814,1302 @@
       <c r="AE14" s="7" t="n"/>
     </row>
     <row r="15" ht="60" customHeight="1">
-      <c r="A15" s="10" t="inlineStr"/>
-      <c r="B15" s="10" t="inlineStr"/>
-      <c r="C15" s="10" t="inlineStr"/>
-      <c r="D15" s="10" t="inlineStr"/>
-      <c r="E15" s="10" t="inlineStr"/>
-      <c r="F15" s="10" t="inlineStr"/>
-      <c r="G15" s="10" t="inlineStr"/>
-      <c r="H15" s="10" t="inlineStr"/>
-      <c r="I15" s="10" t="inlineStr"/>
-      <c r="J15" s="10" t="inlineStr"/>
-      <c r="K15" s="10" t="inlineStr"/>
-      <c r="L15" s="10" t="inlineStr"/>
-      <c r="M15" s="10" t="inlineStr"/>
-      <c r="N15" s="10" t="inlineStr"/>
-      <c r="O15" s="10" t="inlineStr"/>
-      <c r="P15" s="10" t="inlineStr"/>
-      <c r="Q15" s="10" t="inlineStr"/>
-      <c r="R15" s="10" t="inlineStr"/>
-      <c r="S15" s="10" t="inlineStr"/>
-      <c r="T15" s="10" t="inlineStr"/>
-      <c r="U15" s="10" t="inlineStr"/>
-      <c r="V15" s="10" t="inlineStr"/>
-      <c r="W15" s="10" t="inlineStr"/>
-      <c r="X15" s="10" t="inlineStr"/>
-      <c r="Y15" s="10" t="inlineStr"/>
-      <c r="Z15" s="10" t="inlineStr"/>
-      <c r="AA15" s="10" t="inlineStr">
+      <c r="A15" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>1.3/29</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Клапан обратный 19с76нж Ду 50 Ру 16</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>ГОСТ 33423-2015</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>- до 425 ºC</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>вода</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>сталь 25Л, 20, 20Х13</t>
+        </is>
+      </c>
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t>У1</t>
+        </is>
+      </c>
+      <c r="L15" s="6" t="inlineStr">
+        <is>
+          <t>Фланец-фланец</t>
+        </is>
+      </c>
+      <c r="M15" s="6" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="N15" s="6" t="inlineStr"/>
+      <c r="O15" s="6" t="inlineStr">
+        <is>
+          <t>на горизонтальном трубопроводе крышкой вверх; на вертикальном – входным патрубком вверх</t>
+        </is>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>Крышка  Ст.20 Захлопка  Ст. 20 Серьга  Ст.20Л-30Л Кронштейн, ось  Ст. 20Х13 Уплотнение затвора  Наплавленная коррозионно-стойкая сталь 08Х20Н9Г7Т</t>
+        </is>
+      </c>
+      <c r="Q15" s="6" t="inlineStr"/>
+      <c r="R15" s="6" t="inlineStr"/>
+      <c r="S15" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="U15" s="7" t="n"/>
+      <c r="V15" s="8" t="inlineStr">
+        <is>
+          <t>АО «Благовещенский арматурный завод»</t>
+        </is>
+      </c>
+      <c r="W15" s="8" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="X15" s="8" t="inlineStr">
+        <is>
+          <t>10329682</t>
+        </is>
+      </c>
+      <c r="Y15" s="8" t="inlineStr">
+        <is>
+          <t>16.09.2030</t>
+        </is>
+      </c>
+      <c r="Z15" s="7" t="n"/>
+      <c r="AA15" s="9" t="n"/>
+      <c r="AB15" s="10">
+        <f>AA15*S15</f>
+        <v/>
+      </c>
+      <c r="AC15" s="7" t="n"/>
+      <c r="AD15" s="7" t="n"/>
+      <c r="AE15" s="7" t="n"/>
+    </row>
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>1.3/41</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Клапан ВДХ Ду 80 Ру 10</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Класс герметичности по ГОСТ 54808"А"</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>До + 60°С</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>Вода; раствор NaOH 30%; Н2SO4 93%</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>углеродистая сталь</t>
+        </is>
+      </c>
+      <c r="K16" s="6" t="inlineStr">
+        <is>
+          <t>У</t>
+        </is>
+      </c>
+      <c r="L16" s="6" t="inlineStr">
+        <is>
+          <t>Присоединение фланцевое по ГОСТ 12815-80</t>
+        </is>
+      </c>
+      <c r="M16" s="6" t="inlineStr">
+        <is>
+          <t>Ручное</t>
+        </is>
+      </c>
+      <c r="N16" s="6" t="inlineStr">
+        <is>
+          <t>маховик</t>
+        </is>
+      </c>
+      <c r="O16" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>Материал защитного покрытия-фторопласт Ф-4МБ. Мембраны-фторопласт</t>
+        </is>
+      </c>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>строительная длина  310 мм</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr"/>
+      <c r="S16" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="U16" s="7" t="n"/>
+      <c r="V16" s="7" t="n"/>
+      <c r="W16" s="7" t="n"/>
+      <c r="X16" s="7" t="n"/>
+      <c r="Y16" s="7" t="n"/>
+      <c r="Z16" s="7" t="n"/>
+      <c r="AA16" s="9" t="n"/>
+      <c r="AB16" s="10">
+        <f>AA16*S16</f>
+        <v/>
+      </c>
+      <c r="AC16" s="7" t="n"/>
+      <c r="AD16" s="7" t="n"/>
+      <c r="AE16" s="7" t="n"/>
+    </row>
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>1.3/42</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Клапан диафрагменный химический ВДХ Ду 150 Ру 16</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Класс герметичности по ГОСТ 54808"А"</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>До + 60°С</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>Вода; раствор NaOH 30%; Н2SO4 93%</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>углеродистая сталь</t>
+        </is>
+      </c>
+      <c r="K17" s="6" t="inlineStr">
+        <is>
+          <t>У</t>
+        </is>
+      </c>
+      <c r="L17" s="6" t="inlineStr">
+        <is>
+          <t>Присоединение фланцевое по ГОСТ 12815-80</t>
+        </is>
+      </c>
+      <c r="M17" s="6" t="inlineStr">
+        <is>
+          <t>Ручное</t>
+        </is>
+      </c>
+      <c r="N17" s="6" t="inlineStr">
+        <is>
+          <t>маховик</t>
+        </is>
+      </c>
+      <c r="O17" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P17" s="6" t="inlineStr">
+        <is>
+          <t>Материал защитного покрытия-фторопласт Ф-4МБ. Мембраны-фторопласт</t>
+        </is>
+      </c>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>строительная длина  460 мм</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr"/>
+      <c r="S17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="U17" s="7" t="n"/>
+      <c r="V17" s="7" t="n"/>
+      <c r="W17" s="7" t="n"/>
+      <c r="X17" s="7" t="n"/>
+      <c r="Y17" s="7" t="n"/>
+      <c r="Z17" s="7" t="n"/>
+      <c r="AA17" s="9" t="n"/>
+      <c r="AB17" s="10">
+        <f>AA17*S17</f>
+        <v/>
+      </c>
+      <c r="AC17" s="7" t="n"/>
+      <c r="AD17" s="7" t="n"/>
+      <c r="AE17" s="7" t="n"/>
+    </row>
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>1.3/43</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Клапан диафрагменный химический ВДХ Ду 50, Ру 16</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>Класс герметичности по ГОСТ 54808"А"</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>от -50 до +150°С</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>любые жидкие реагенты и химические среды.</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>углеродистая сталь</t>
+        </is>
+      </c>
+      <c r="K18" s="6" t="inlineStr">
+        <is>
+          <t>У</t>
+        </is>
+      </c>
+      <c r="L18" s="6" t="inlineStr">
+        <is>
+          <t>Присоединение фланцевое по ГОСТ 12815-80</t>
+        </is>
+      </c>
+      <c r="M18" s="6" t="inlineStr">
+        <is>
+          <t>Ручное</t>
+        </is>
+      </c>
+      <c r="N18" s="6" t="inlineStr">
+        <is>
+          <t>маховик</t>
+        </is>
+      </c>
+      <c r="O18" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P18" s="6" t="inlineStr">
+        <is>
+          <t>Материал защитного покрытия-фторопласт Ф-4МБ. Мембраны-фторопласт</t>
+        </is>
+      </c>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>строительная длина  210 мм,</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr"/>
+      <c r="S18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="U18" s="7" t="n"/>
+      <c r="V18" s="7" t="n"/>
+      <c r="W18" s="7" t="n"/>
+      <c r="X18" s="7" t="n"/>
+      <c r="Y18" s="7" t="n"/>
+      <c r="Z18" s="7" t="n"/>
+      <c r="AA18" s="9" t="n"/>
+      <c r="AB18" s="10">
+        <f>AA18*S18</f>
+        <v/>
+      </c>
+      <c r="AC18" s="7" t="n"/>
+      <c r="AD18" s="7" t="n"/>
+      <c r="AE18" s="7" t="n"/>
+    </row>
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>1.3/44</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Клапан диафрагменный химический ВДХ Ду 80 Ру 16</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Класс герметичности по ГОСТ 54808"А"</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>от -50 до +150°С</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>любые жидкие реагенты и химические среды.</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>углеродистая сталь</t>
+        </is>
+      </c>
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t>У</t>
+        </is>
+      </c>
+      <c r="L19" s="6" t="inlineStr">
+        <is>
+          <t>Присоединение фланцевое по ГОСТ 12815-80</t>
+        </is>
+      </c>
+      <c r="M19" s="6" t="inlineStr">
+        <is>
+          <t>Ручное</t>
+        </is>
+      </c>
+      <c r="N19" s="6" t="inlineStr">
+        <is>
+          <t>маховик</t>
+        </is>
+      </c>
+      <c r="O19" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P19" s="6" t="inlineStr">
+        <is>
+          <t>Материал защитного покрытия-фторопласт Ф-4МБ. Мембраны-фторопласт</t>
+        </is>
+      </c>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>строительная длина  310 мм,</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr"/>
+      <c r="S19" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="U19" s="7" t="n"/>
+      <c r="V19" s="7" t="n"/>
+      <c r="W19" s="7" t="n"/>
+      <c r="X19" s="7" t="n"/>
+      <c r="Y19" s="7" t="n"/>
+      <c r="Z19" s="7" t="n"/>
+      <c r="AA19" s="9" t="n"/>
+      <c r="AB19" s="10">
+        <f>AA19*S19</f>
+        <v/>
+      </c>
+      <c r="AC19" s="7" t="n"/>
+      <c r="AD19" s="7" t="n"/>
+      <c r="AE19" s="7" t="n"/>
+    </row>
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>1.3/63</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Клапан запорный 15с52нж11 Ду 20 Ру 63 под приварку</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>ГОСТ 9697-87</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>до + 425°С</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>вода, слабоагрессивные жидкие среды</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>Сталь 25 Л</t>
+        </is>
+      </c>
+      <c r="K20" s="6" t="inlineStr">
+        <is>
+          <t>У1</t>
+        </is>
+      </c>
+      <c r="L20" s="6" t="inlineStr">
+        <is>
+          <t>под приварку</t>
+        </is>
+      </c>
+      <c r="M20" s="6" t="inlineStr">
+        <is>
+          <t>ручное</t>
+        </is>
+      </c>
+      <c r="N20" s="6" t="inlineStr">
+        <is>
+          <t>маховик, рукоятка</t>
+        </is>
+      </c>
+      <c r="O20" s="6" t="inlineStr">
+        <is>
+          <t>любом рабочем положении</t>
+        </is>
+      </c>
+      <c r="P20" s="6" t="inlineStr">
+        <is>
+          <t>Материал корпуса, диска, крышки: сталь 25
+Материал седла, шпинделя: нержавеющая сталь</t>
+        </is>
+      </c>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr"/>
+      <c r="S20" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="T20" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="U20" s="7" t="n"/>
+      <c r="V20" s="7" t="n"/>
+      <c r="W20" s="7" t="n"/>
+      <c r="X20" s="7" t="n"/>
+      <c r="Y20" s="7" t="n"/>
+      <c r="Z20" s="7" t="n"/>
+      <c r="AA20" s="9" t="n"/>
+      <c r="AB20" s="10">
+        <f>AA20*S20</f>
+        <v/>
+      </c>
+      <c r="AC20" s="7" t="n"/>
+      <c r="AD20" s="7" t="n"/>
+      <c r="AE20" s="7" t="n"/>
+    </row>
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>1.3/67</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>Клапан запорный 15ч93эм Ду 20 Ру 16</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>ТУ 26-07-1051-84</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>От -15°С до +120°С</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>Агрессивная</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>Серый чугун СЧ18</t>
+        </is>
+      </c>
+      <c r="K21" s="6" t="inlineStr">
+        <is>
+          <t>УХЛ4</t>
+        </is>
+      </c>
+      <c r="L21" s="6" t="inlineStr">
+        <is>
+          <t>фланец-фланец</t>
+        </is>
+      </c>
+      <c r="M21" s="6" t="inlineStr">
+        <is>
+          <t>ручное</t>
+        </is>
+      </c>
+      <c r="N21" s="6" t="inlineStr">
+        <is>
+          <t>маховик</t>
+        </is>
+      </c>
+      <c r="O21" s="6" t="inlineStr">
+        <is>
+          <t>любое</t>
+        </is>
+      </c>
+      <c r="P21" s="6" t="inlineStr">
+        <is>
+          <t>Корпус: чугун.
+Крышка: чугун.
+Шпиндель: сталь.
+Крестовина: чугун.
+Диафрагма: фторопласт-4.</t>
+        </is>
+      </c>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>L-150мм, Н-146мм</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr"/>
+      <c r="S21" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="U21" s="7" t="n"/>
+      <c r="V21" s="7" t="n"/>
+      <c r="W21" s="7" t="n"/>
+      <c r="X21" s="7" t="n"/>
+      <c r="Y21" s="7" t="n"/>
+      <c r="Z21" s="7" t="n"/>
+      <c r="AA21" s="9" t="n"/>
+      <c r="AB21" s="10">
+        <f>AA21*S21</f>
+        <v/>
+      </c>
+      <c r="AC21" s="7" t="n"/>
+      <c r="AD21" s="7" t="n"/>
+      <c r="AE21" s="7" t="n"/>
+    </row>
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>1.6/12</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Клапан предохранительный 17с28нж Ду 50 Ру16 (Рн 10-16)</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>ТУ 3742-003-22294686-2007</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>от -40 до +425</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>вода, воздух, пар, аммиак, природный газ, нефть, нефтепродукты</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>сталь 25Л</t>
+        </is>
+      </c>
+      <c r="K22" s="6" t="inlineStr">
+        <is>
+          <t>У1</t>
+        </is>
+      </c>
+      <c r="L22" s="6" t="inlineStr">
+        <is>
+          <t>фланцевый</t>
+        </is>
+      </c>
+      <c r="M22" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O22" s="6" t="inlineStr">
+        <is>
+          <t>вертикальное, колпаком вверх</t>
+        </is>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t>Уплотнение в затворе - нержавеющая сталь; Пружина - Сталь 50ХФА; Золотник, седло, шток - Сталь 20Х13</t>
+        </is>
+      </c>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S22" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="T22" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="U22" s="7" t="n"/>
+      <c r="V22" s="8" t="inlineStr">
+        <is>
+          <t>АО «Благовещенский арматурный завод»</t>
+        </is>
+      </c>
+      <c r="W22" s="8" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="X22" s="8" t="inlineStr">
+        <is>
+          <t>10329690</t>
+        </is>
+      </c>
+      <c r="Y22" s="8" t="inlineStr">
+        <is>
+          <t>16.09.2030</t>
+        </is>
+      </c>
+      <c r="Z22" s="7" t="n"/>
+      <c r="AA22" s="9" t="n"/>
+      <c r="AB22" s="10">
+        <f>AA22*S22</f>
+        <v/>
+      </c>
+      <c r="AC22" s="7" t="n"/>
+      <c r="AD22" s="7" t="n"/>
+      <c r="AE22" s="7" t="n"/>
+    </row>
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>1.6/13</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Клапан предохранительный 17с6нж Ду 50 Ру 16</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>ТУ 3742-005-22294686-2009</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>от -40 до +425</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>жидкие и газообразные, нефть, нефтепродукты, углеводородные газы, вода, пар</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>сталь 25Л</t>
+        </is>
+      </c>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
+          <t>У1</t>
+        </is>
+      </c>
+      <c r="L23" s="6" t="inlineStr">
+        <is>
+          <t>фланцевый</t>
+        </is>
+      </c>
+      <c r="M23" s="6" t="inlineStr"/>
+      <c r="N23" s="6" t="inlineStr"/>
+      <c r="O23" s="6" t="inlineStr">
+        <is>
+          <t>вертикальное, колпаком вверх</t>
+        </is>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
+        <is>
+          <t>Седло: сталь 20Х13
+Шток: сталь 20Х13.
+Пружина: 50ХФА
+Прокладка: Паронит
+Шпилька: сталь 35</t>
+        </is>
+      </c>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S23" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T23" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="U23" s="7" t="n"/>
+      <c r="V23" s="8" t="inlineStr">
+        <is>
+          <t>АО «Благовещенский арматурный завод»</t>
+        </is>
+      </c>
+      <c r="W23" s="8" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="X23" s="8" t="inlineStr">
+        <is>
+          <t>10329690</t>
+        </is>
+      </c>
+      <c r="Y23" s="8" t="inlineStr">
+        <is>
+          <t>16.09.2030</t>
+        </is>
+      </c>
+      <c r="Z23" s="7" t="n"/>
+      <c r="AA23" s="9" t="n"/>
+      <c r="AB23" s="10">
+        <f>AA23*S23</f>
+        <v/>
+      </c>
+      <c r="AC23" s="7" t="n"/>
+      <c r="AD23" s="7" t="n"/>
+      <c r="AE23" s="7" t="n"/>
+    </row>
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>1.6/14</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>Клапан предохранительный 17с6нж Ду 80 Ру 16</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>ТУ 3742-005-22294686-2009</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>от -40 до +425</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>жидкие и газообразные, нефть, нефтепродукты, углеводородные газы, вода, пар</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>сталь 25Л</t>
+        </is>
+      </c>
+      <c r="K24" s="6" t="inlineStr">
+        <is>
+          <t>У1</t>
+        </is>
+      </c>
+      <c r="L24" s="6" t="inlineStr">
+        <is>
+          <t>фланцевый</t>
+        </is>
+      </c>
+      <c r="M24" s="6" t="inlineStr"/>
+      <c r="N24" s="6" t="inlineStr"/>
+      <c r="O24" s="6" t="inlineStr">
+        <is>
+          <t>вертикальное, колпаком вверх</t>
+        </is>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>Седло: сталь 20Х13
+Шток: сталь 20Х13.
+Пружина: 50ХФА
+Прокладка: Паронит
+Шпилька: сталь 35</t>
+        </is>
+      </c>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S24" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="U24" s="7" t="n"/>
+      <c r="V24" s="8" t="inlineStr">
+        <is>
+          <t>АО «Благовещенский арматурный завод»</t>
+        </is>
+      </c>
+      <c r="W24" s="8" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="X24" s="8" t="inlineStr">
+        <is>
+          <t>10329690</t>
+        </is>
+      </c>
+      <c r="Y24" s="8" t="inlineStr">
+        <is>
+          <t>16.09.2030</t>
+        </is>
+      </c>
+      <c r="Z24" s="7" t="n"/>
+      <c r="AA24" s="9" t="n"/>
+      <c r="AB24" s="10">
+        <f>AA24*S24</f>
+        <v/>
+      </c>
+      <c r="AC24" s="7" t="n"/>
+      <c r="AD24" s="7" t="n"/>
+      <c r="AE24" s="7" t="n"/>
+    </row>
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>1.6/20</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>Клапан запорный 15кч12пМ Ду 25 Ру 25</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>ТУ 3732-001-00218137-94</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>от -40 до +150</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>Хладон, аммиак, вода, пар</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>ковкий чугун КЧ 30-6</t>
+        </is>
+      </c>
+      <c r="K25" s="6" t="inlineStr">
+        <is>
+          <t>УХЛ4 Температура окружающей среды от - 30 до +50</t>
+        </is>
+      </c>
+      <c r="L25" s="6" t="inlineStr">
+        <is>
+          <t>фланцевый</t>
+        </is>
+      </c>
+      <c r="M25" s="6" t="inlineStr">
+        <is>
+          <t>ручной (маховик)</t>
+        </is>
+      </c>
+      <c r="N25" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O25" s="6" t="inlineStr">
+        <is>
+          <t>любое</t>
+        </is>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>Золотник, шпиндель - сталь;
+Уплотнение - Фторопласт-4</t>
+        </is>
+      </c>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="U25" s="7" t="n"/>
+      <c r="V25" s="7" t="n"/>
+      <c r="W25" s="7" t="n"/>
+      <c r="X25" s="7" t="n"/>
+      <c r="Y25" s="7" t="n"/>
+      <c r="Z25" s="7" t="n"/>
+      <c r="AA25" s="9" t="n"/>
+      <c r="AB25" s="10">
+        <f>AA25*S25</f>
+        <v/>
+      </c>
+      <c r="AC25" s="7" t="n"/>
+      <c r="AD25" s="7" t="n"/>
+      <c r="AE25" s="7" t="n"/>
+    </row>
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" s="11" t="inlineStr"/>
+      <c r="B26" s="11" t="inlineStr"/>
+      <c r="C26" s="11" t="inlineStr"/>
+      <c r="D26" s="11" t="inlineStr"/>
+      <c r="E26" s="11" t="inlineStr"/>
+      <c r="F26" s="11" t="inlineStr"/>
+      <c r="G26" s="11" t="inlineStr"/>
+      <c r="H26" s="11" t="inlineStr"/>
+      <c r="I26" s="11" t="inlineStr"/>
+      <c r="J26" s="11" t="inlineStr"/>
+      <c r="K26" s="11" t="inlineStr"/>
+      <c r="L26" s="11" t="inlineStr"/>
+      <c r="M26" s="11" t="inlineStr"/>
+      <c r="N26" s="11" t="inlineStr"/>
+      <c r="O26" s="11" t="inlineStr"/>
+      <c r="P26" s="11" t="inlineStr"/>
+      <c r="Q26" s="11" t="inlineStr"/>
+      <c r="R26" s="11" t="inlineStr"/>
+      <c r="S26" s="11" t="inlineStr"/>
+      <c r="T26" s="11" t="inlineStr"/>
+      <c r="U26" s="11" t="inlineStr"/>
+      <c r="V26" s="11" t="inlineStr"/>
+      <c r="W26" s="11" t="inlineStr"/>
+      <c r="X26" s="11" t="inlineStr"/>
+      <c r="Y26" s="11" t="inlineStr"/>
+      <c r="Z26" s="11" t="inlineStr"/>
+      <c r="AA26" s="11" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="AB15" s="11">
-        <f>SUM(AB6:AB14)</f>
+      <c r="AB26" s="12">
+        <f>SUM(AB6:AB25)</f>
         <v/>
       </c>
-      <c r="AC15" s="2" t="n"/>
-      <c r="AD15" s="2" t="n"/>
-      <c r="AE15" s="2" t="n"/>
+      <c r="AC26" s="2" t="n"/>
+      <c r="AD26" s="2" t="n"/>
+      <c r="AE26" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
